--- a/data/orderInfo.xlsx
+++ b/data/orderInfo.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="16">
   <si>
     <t>productOrderName</t>
   </si>
@@ -56,6 +56,12 @@
   </si>
   <si>
     <t>2025-11-27 20-16-17</t>
+  </si>
+  <si>
+    <t>chicken burger</t>
+  </si>
+  <si>
+    <t>2025-11-30 15:41:47</t>
   </si>
 </sst>
 </file>
@@ -365,7 +371,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -487,6 +493,23 @@
         <v>13</v>
       </c>
     </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8">
+        <v>2.5</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
+      <c r="D8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
